--- a/Day 3/whatsapp_report_2026-08-26.xlsx
+++ b/Day 3/whatsapp_report_2026-08-26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai\GenAIArchitect\Day 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1807A7B0-D0A9-48B5-B4B4-0BCDF04C0FCA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1684C94C-95D3-412E-AD00-FAEFE91E2010}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,9 +49,6 @@
     <t>Jo</t>
   </si>
   <si>
-    <t>919500182664</t>
-  </si>
-  <si>
     <t>sent_unconfirmed</t>
   </si>
   <si>
@@ -67,9 +64,6 @@
     <t>Sankar</t>
   </si>
   <si>
-    <t>919790197977</t>
-  </si>
-  <si>
     <t>2026-08-26 12:05:45</t>
   </si>
   <si>
@@ -77,6 +71,12 @@
   </si>
   <si>
     <t>screenshots\Sankar_2026-08-26.png</t>
+  </si>
+  <si>
+    <t>919876543210</t>
+  </si>
+  <si>
+    <t>910987654321</t>
   </si>
 </sst>
 </file>
@@ -112,8 +112,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -457,43 +458,44 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>